--- a/data/trans_orig/IP07A09-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07A09-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2007 (tasa de respuesta: 99,5%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a, percibida por el adulto en 2007 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>558</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14980</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11359</t>
+          <t>11287</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23153</t>
+          <t>23319</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19613</t>
+          <t>19019</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35493</t>
+          <t>34460</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15305</t>
+          <t>14763</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28549</t>
+          <t>27847</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20526</t>
+          <t>20313</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34236</t>
+          <t>33657</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39539</t>
+          <t>39146</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>57650</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,8%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24453</t>
+          <t>25507</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38057</t>
+          <t>39083</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28322</t>
+          <t>28724</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43216</t>
+          <t>43144</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56995</t>
+          <t>58396</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76562</t>
+          <t>76956</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>53,13%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>626</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>682</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>20438</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9827</t>
+          <t>9191</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20891</t>
+          <t>21027</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20956</t>
+          <t>21604</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36866</t>
+          <t>36829</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21300</t>
+          <t>20731</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35436</t>
+          <t>35221</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22793</t>
+          <t>23115</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37327</t>
+          <t>37973</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47476</t>
+          <t>47546</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66906</t>
+          <t>67394</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50831</t>
+          <t>50159</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66963</t>
+          <t>66846</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45307</t>
+          <t>44714</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60650</t>
+          <t>60687</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>102095</t>
+          <t>100824</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124302</t>
+          <t>121990</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>60,22%</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>717</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>6244</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7963</t>
+          <t>8382</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17874</t>
+          <t>18122</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>8532</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18269</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>18443</t>
+          <t>19511</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>32895</t>
+          <t>33522</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>12113</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22798</t>
+          <t>22977</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10667</t>
+          <t>10487</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21720</t>
+          <t>21572</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25256</t>
+          <t>25457</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40123</t>
+          <t>40300</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23402</t>
+          <t>23145</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35429</t>
+          <t>35084</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29504</t>
+          <t>29107</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42524</t>
+          <t>42216</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57279</t>
+          <t>57045</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74781</t>
+          <t>74701</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,66%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>717</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7127</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>799</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7311</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9660</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13606</t>
+          <t>13420</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27220</t>
+          <t>27190</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>9810</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21095</t>
+          <t>21594</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>26890</t>
+          <t>26401</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>43964</t>
+          <t>45093</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,59%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>12979</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26701</t>
+          <t>26686</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14607</t>
+          <t>15589</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27940</t>
+          <t>28261</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32744</t>
+          <t>31930</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51362</t>
+          <t>50773</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>40309</t>
+          <t>40269</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>56756</t>
+          <t>56344</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>51883</t>
+          <t>52284</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67264</t>
+          <t>67939</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>97054</t>
+          <t>96122</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>118837</t>
+          <t>118495</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>61,98%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>12925</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13065</t>
+          <t>12885</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>9226</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>19302</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>46223</t>
+          <t>45696</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>67305</t>
+          <t>66725</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>47485</t>
+          <t>48563</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>69518</t>
+          <t>71517</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>99594</t>
+          <t>99149</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>130611</t>
+          <t>132525</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>74085</t>
+          <t>74072</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>100227</t>
+          <t>100925</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>81055</t>
+          <t>80532</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>107756</t>
+          <t>107787</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>161759</t>
+          <t>159308</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>198500</t>
+          <t>197985</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>153085</t>
+          <t>152642</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>182132</t>
+          <t>181542</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>168651</t>
+          <t>169518</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>199313</t>
+          <t>199292</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>332172</t>
+          <t>332759</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>374275</t>
+          <t>373044</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,02%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>916</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7567</t>
+          <t>7490</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>6835</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17075</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9287</t>
+          <t>9576</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21747</t>
+          <t>21441</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18639</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34454</t>
+          <t>34618</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11498</t>
+          <t>11168</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22968</t>
+          <t>23086</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>8712</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20439</t>
+          <t>19750</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23194</t>
+          <t>22283</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39213</t>
+          <t>38437</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27538</t>
+          <t>27110</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40873</t>
+          <t>40761</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34864</t>
+          <t>34851</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>49452</t>
+          <t>48832</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>66989</t>
+          <t>66678</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>86653</t>
+          <t>85891</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,11%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6060</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>781</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6509</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2674</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10138</t>
+          <t>10376</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8895</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14004</t>
+          <t>14614</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27389</t>
+          <t>26578</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15733</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28109</t>
+          <t>28062</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32564</t>
+          <t>32029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50812</t>
+          <t>49378</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19226</t>
+          <t>19771</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33478</t>
+          <t>33936</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22506</t>
+          <t>22143</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32782</t>
+          <t>33004</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51223</t>
+          <t>51186</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39633</t>
+          <t>39421</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56275</t>
+          <t>55796</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45925</t>
+          <t>46786</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61842</t>
+          <t>61996</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91766</t>
+          <t>92261</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>113853</t>
+          <t>113936</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,21%</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6891</t>
+          <t>6778</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>3553</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>596</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6044</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>6661</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16549</t>
+          <t>16531</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18060</t>
+          <t>18024</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16716</t>
+          <t>17020</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31346</t>
+          <t>30955</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25340</t>
+          <t>26010</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>7559</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17326</t>
+          <t>17291</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23828</t>
+          <t>24298</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39770</t>
+          <t>40142</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25280</t>
+          <t>26047</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38469</t>
+          <t>39081</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35378</t>
+          <t>35560</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48231</t>
+          <t>48147</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>65516</t>
+          <t>65437</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>84115</t>
+          <t>84386</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,36%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>11488</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>12066</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>836</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>7806</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13058</t>
+          <t>12803</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13440</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27707</t>
+          <t>27312</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13876</t>
+          <t>13720</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28368</t>
+          <t>27161</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31150</t>
+          <t>31519</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>50157</t>
+          <t>50358</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,4%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12498</t>
+          <t>12184</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25364</t>
+          <t>25343</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18516</t>
+          <t>19485</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33763</t>
+          <t>34308</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34949</t>
+          <t>35420</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>55384</t>
+          <t>55467</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,18%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35590</t>
+          <t>35673</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>52590</t>
+          <t>51827</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33319</t>
+          <t>33186</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>49220</t>
+          <t>49542</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>73674</t>
+          <t>73202</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>96537</t>
+          <t>96908</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,72%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17908</t>
+          <t>18008</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>9161</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10113</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23405</t>
+          <t>23508</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>16089</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16288</t>
+          <t>15871</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12823</t>
+          <t>12692</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>27026</t>
+          <t>27010</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>51340</t>
+          <t>51275</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>74907</t>
+          <t>75917</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>57180</t>
+          <t>57721</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>81200</t>
+          <t>81667</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>114564</t>
+          <t>115080</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>148332</t>
+          <t>149661</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>67463</t>
+          <t>67223</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>92260</t>
+          <t>92671</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>56556</t>
+          <t>56303</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>81069</t>
+          <t>80081</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>132123</t>
+          <t>132114</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>166518</t>
+          <t>168183</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>144735</t>
+          <t>144453</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>173962</t>
+          <t>173556</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>165431</t>
+          <t>164193</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>194380</t>
+          <t>195152</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>316022</t>
+          <t>316210</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>358680</t>
+          <t>358429</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>54,88%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse harto en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de sentirse harto/a, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>731</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>6232</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>884</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11727</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7972</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>725</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6370</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10917</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18454</t>
+          <t>17653</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10506</t>
+          <t>10488</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23022</t>
+          <t>22402</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19409</t>
+          <t>20265</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36630</t>
+          <t>35552</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13316</t>
+          <t>14293</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26732</t>
+          <t>26993</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>15817</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29438</t>
+          <t>28895</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33056</t>
+          <t>32686</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52314</t>
+          <t>50868</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,21%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26319</t>
+          <t>26736</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41080</t>
+          <t>41156</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23141</t>
+          <t>23809</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38344</t>
+          <t>38262</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>54643</t>
+          <t>54315</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>74454</t>
+          <t>73806</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,09%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>576</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>659</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6124</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11978</t>
+          <t>11974</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>798</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6312</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16231</t>
+          <t>16802</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13288</t>
+          <t>13537</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26121</t>
+          <t>25269</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11836</t>
+          <t>12259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24188</t>
+          <t>24705</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28546</t>
+          <t>28331</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46310</t>
+          <t>46769</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27285</t>
+          <t>27450</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43401</t>
+          <t>43093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21365</t>
+          <t>21159</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35592</t>
+          <t>36153</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53365</t>
+          <t>53560</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74280</t>
+          <t>75147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35204</t>
+          <t>35284</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51389</t>
+          <t>52042</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47722</t>
+          <t>47644</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64393</t>
+          <t>64311</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>87569</t>
+          <t>87197</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>110702</t>
+          <t>110028</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,48%</t>
         </is>
       </c>
     </row>
@@ -9385,7 +9385,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>703</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7005</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18272</t>
+          <t>18191</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19104</t>
+          <t>19356</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>18668</t>
+          <t>18434</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>32998</t>
+          <t>32765</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18795</t>
+          <t>18466</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>9515</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21685</t>
+          <t>22034</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20864</t>
+          <t>20323</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36349</t>
+          <t>36650</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37183</t>
+          <t>37149</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49970</t>
+          <t>50144</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38347</t>
+          <t>39152</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53758</t>
+          <t>53298</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81255</t>
+          <t>80107</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100807</t>
+          <t>100420</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,1%</t>
         </is>
       </c>
     </row>
@@ -10067,7 +10067,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7985</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9751</t>
+          <t>9093</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>11171</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>15838</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30340</t>
+          <t>30181</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19662</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33807</t>
+          <t>34382</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>38896</t>
+          <t>39068</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>58930</t>
+          <t>58697</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25003</t>
+          <t>25150</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41544</t>
+          <t>42467</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22528</t>
+          <t>20732</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37535</t>
+          <t>37357</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>52505</t>
+          <t>52936</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>74500</t>
+          <t>74554</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,55%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37005</t>
+          <t>37359</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55914</t>
+          <t>55431</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34411</t>
+          <t>34049</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51022</t>
+          <t>51225</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>76618</t>
+          <t>76534</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>100478</t>
+          <t>100410</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,88%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>13223</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>14775</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10856</t>
+          <t>10789</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24576</t>
+          <t>24482</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9653</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>23160</t>
+          <t>22865</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5620</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>15181</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>17356</t>
+          <t>17744</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>33937</t>
+          <t>34297</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>54487</t>
+          <t>55157</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>78602</t>
+          <t>78490</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>60867</t>
+          <t>59969</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>86051</t>
+          <t>84510</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>120513</t>
+          <t>121787</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>156118</t>
+          <t>156642</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>87837</t>
+          <t>87630</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>116149</t>
+          <t>115993</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>80971</t>
+          <t>82815</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>109629</t>
+          <t>109701</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>175493</t>
+          <t>176758</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>215735</t>
+          <t>217771</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>150878</t>
+          <t>150191</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>183520</t>
+          <t>183003</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>159580</t>
+          <t>159487</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>191269</t>
+          <t>192044</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>320986</t>
+          <t>319149</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>366775</t>
+          <t>363224</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>50,62%</t>
         </is>
       </c>
     </row>
